--- a/CLIENT/DATExx-Whiddon/2. Calculations/EOW/Boundary Intersections.xlsx
+++ b/CLIENT/DATExx-Whiddon/2. Calculations/EOW/Boundary Intersections.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://resrodel-my.sharepoint.com/personal/alex_james_resrodel_com/Documents/RESRODEL/2. Product/2.5 Engineering/Resro.OPT/2D/Config3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\CentriNOTSYNC\ResidentialCare\CLIENT\DATExx-Whiddon\2. Calculations\EOW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{A807137C-63EC-41BA-89F1-144C726D2DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BA4D4F7-41E9-480C-A056-EC4B8AC953B4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9E677D-F3C3-477D-A0EE-9CB90AAFF68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="990" yWindow="75" windowWidth="26415" windowHeight="20295" activeTab="1" xr2:uid="{1A6D2DB0-E7C1-4601-8836-610F057FFD94}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{1A6D2DB0-E7C1-4601-8836-610F057FFD94}"/>
   </bookViews>
   <sheets>
     <sheet name="Thresholds" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -768,9 +769,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -808,7 +809,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -914,7 +915,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1056,7 +1057,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1869,7 +1870,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="6">
-        <f t="shared" ref="I8:J8" si="0">O8</f>
+        <f t="shared" ref="I8" si="0">O8</f>
         <v>0</v>
       </c>
       <c r="J8" s="6">
@@ -2330,15 +2331,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82d1b6b-c0e6-44b0-99a2-d357b2d50896">
@@ -2349,14 +2341,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF0E510C-DAFC-499D-8861-67F938824D02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF0E510C-DAFC-499D-8861-67F938824D02}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f82d1b6b-c0e6-44b0-99a2-d357b2d50896"/>
+    <ds:schemaRef ds:uri="3be0b85a-8471-4f10-b038-505fde09e598"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBCABA90-1AD3-4D5B-B87D-776F5546314E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE86E99-E03C-4C87-82BA-42F178247D02}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f82d1b6b-c0e6-44b0-99a2-d357b2d50896"/>
+    <ds:schemaRef ds:uri="3be0b85a-8471-4f10-b038-505fde09e598"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EE86E99-E03C-4C87-82BA-42F178247D02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBCABA90-1AD3-4D5B-B87D-776F5546314E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>